--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 17:18</t>
+          <t>更新时间: 2026-09-14 09:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 09:33</t>
+          <t>更新时间: 2026-09-14 12:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 12:59</t>
+          <t>更新时间: 2026-09-14 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 13:36</t>
+          <t>更新时间: 2026-09-14 15:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 15:57</t>
+          <t>更新时间: 2026-09-14 17:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 17:40</t>
+          <t>更新时间: 2026-09-15 09:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 09:51</t>
+          <t>更新时间: 2026-09-15 12:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 12:57</t>
+          <t>更新时间: 2026-09-15 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 13:38</t>
+          <t>更新时间: 2026-09-15 15:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 15:51</t>
+          <t>更新时间: 2026-09-15 17:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 17:16</t>
+          <t>更新时间: 2026-09-16 09:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 09:38</t>
+          <t>更新时间: 2026-09-16 12:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 12:52</t>
+          <t>更新时间: 2026-09-16 13:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:32</t>
+          <t>更新时间: 2026-09-16 15:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 15:45</t>
+          <t>更新时间: 2026-09-16 17:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 17:09</t>
+          <t>更新时间: 2026-09-17 09:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 09:42</t>
+          <t>更新时间: 2026-09-17 12:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 12:55</t>
+          <t>更新时间: 2026-09-17 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:38</t>
+          <t>更新时间: 2026-09-17 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 15:46</t>
+          <t>更新时间: 2026-09-17 17:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 17:17</t>
+          <t>更新时间: 2026-09-18 09:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 09:29</t>
+          <t>更新时间: 2026-09-18 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 12:47</t>
+          <t>更新时间: 2026-09-18 13:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:26</t>
+          <t>更新时间: 2026-09-18 15:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 15:27</t>
+          <t>更新时间: 2026-09-18 16:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 16:52</t>
+          <t>更新时间: 2026-09-19 09:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:40</t>
+          <t>更新时间: 2026-09-19 12:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 12:40</t>
+          <t>更新时间: 2026-09-19 13:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:22</t>
+          <t>更新时间: 2026-09-19 15:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 15:23</t>
+          <t>更新时间: 2026-09-19 16:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 16:39</t>
+          <t>更新时间: 2026-09-20 09:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 09:32</t>
+          <t>更新时间: 2026-09-20 12:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 12:56</t>
+          <t>更新时间: 2026-09-20 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:35</t>
+          <t>更新时间: 2026-09-20 15:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 15:47</t>
+          <t>更新时间: 2026-09-20 17:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 17:09</t>
+          <t>更新时间: 2026-09-21 09:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:30</t>
+          <t>更新时间: 2026-09-21 12:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 12:58</t>
+          <t>更新时间: 2026-09-21 13:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 13:44</t>
+          <t>更新时间: 2026-09-21 16:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 16:01</t>
+          <t>更新时间: 2026-09-21 17:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 17:45</t>
+          <t>更新时间: 2026-09-22 09:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 09:49</t>
+          <t>更新时间: 2026-09-22 13:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:00</t>
+          <t>更新时间: 2026-09-22 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:42</t>
+          <t>更新时间: 2026-09-22 15:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 15:46</t>
+          <t>更新时间: 2026-09-22 17:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 17:09</t>
+          <t>更新时间: 2026-09-23 09:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:46</t>
+          <t>更新时间: 2026-09-23 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 12:47</t>
+          <t>更新时间: 2026-09-23 13:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:24</t>
+          <t>更新时间: 2026-09-23 15:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 15:49</t>
+          <t>更新时间: 2026-09-23 17:10</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 17:10</t>
+          <t>更新时间: 2026-09-24 09:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 09:47</t>
+          <t>更新时间: 2026-09-24 12:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 12:54</t>
+          <t>更新时间: 2026-09-24 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:43</t>
+          <t>更新时间: 2026-09-24 15:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 15:39</t>
+          <t>更新时间: 2026-09-24 17:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 17:06</t>
+          <t>更新时间: 2026-09-25 09:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 09:52</t>
+          <t>更新时间: 2026-09-25 13:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:00</t>
+          <t>更新时间: 2026-09-25 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:40</t>
+          <t>更新时间: 2026-09-25 15:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 15:56</t>
+          <t>更新时间: 2026-09-25 17:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 17:28</t>
+          <t>更新时间: 2026-09-26 09:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 09:56</t>
+          <t>更新时间: 2026-09-26 13:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:01</t>
+          <t>更新时间: 2026-09-26 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:43</t>
+          <t>更新时间: 2026-09-26 15:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 15:49</t>
+          <t>更新时间: 2026-09-26 17:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 17:13</t>
+          <t>更新时间: 2026-09-27 09:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 09:47</t>
+          <t>更新时间: 2026-09-27 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:21</t>
+          <t>更新时间: 2026-09-27 14:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 14:03</t>
+          <t>更新时间: 2026-09-27 16:19</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 16:19</t>
+          <t>更新时间: 2026-09-27 17:53</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 17:53</t>
+          <t>更新时间: 2026-09-28 10:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 10:02</t>
+          <t>更新时间: 2026-09-28 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 13:27</t>
+          <t>更新时间: 2026-09-28 14:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:11</t>
+          <t>更新时间: 2026-09-28 16:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 16:46</t>
+          <t>更新时间: 2026-09-28 18:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 18:41</t>
+          <t>更新时间: 2026-09-29 10:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 10:45</t>
+          <t>更新时间: 2026-09-29 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 13:46</t>
+          <t>更新时间: 2026-09-29 14:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:28</t>
+          <t>更新时间: 2026-09-29 16:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 16:39</t>
+          <t>更新时间: 2026-09-29 18:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 18:28</t>
+          <t>更新时间: 2026-09-30 10:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 10:25</t>
+          <t>更新时间: 2026-09-30 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 13:35</t>
+          <t>更新时间: 2026-09-30 14:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:13</t>
+          <t>更新时间: 2026-09-30 16:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 16:40</t>
+          <t>更新时间: 2026-09-30 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 18:21</t>
+          <t>更新时间: 2026-10-01 10:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 10:24</t>
+          <t>更新时间: 2026-10-01 13:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 13:59</t>
+          <t>更新时间: 2026-10-01 14:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 14:44</t>
+          <t>更新时间: 2026-10-01 17:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 17:03</t>
+          <t>更新时间: 2026-10-01 18:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 18:47</t>
+          <t>更新时间: 2026-10-02 10:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 10:34</t>
+          <t>更新时间: 2026-10-02 13:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 13:41</t>
+          <t>更新时间: 2026-10-02 14:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:31</t>
+          <t>更新时间: 2026-10-02 16:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 16:38</t>
+          <t>更新时间: 2026-10-02 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 18:21</t>
+          <t>更新时间: 2026-10-03 10:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:25</t>
+          <t>更新时间: 2026-10-03 13:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:21</t>
+          <t>更新时间: 2026-10-03 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:57</t>
+          <t>更新时间: 2026-10-03 16:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 16:15</t>
+          <t>更新时间: 2026-10-03 17:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 17:44</t>
+          <t>更新时间: 2026-10-04 10:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 10:54</t>
+          <t>更新时间: 2026-10-04 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 13:57</t>
+          <t>更新时间: 2026-10-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:33</t>
+          <t>更新时间: 2026-10-04 16:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 16:31</t>
+          <t>更新时间: 2026-10-04 18:27</t>
         </is>
       </c>
     </row>
